--- a/IPPU/A1_Outputs/A-O_Demand.xlsx
+++ b/IPPU/A1_Outputs/A-O_Demand.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IgnacioAlfaroCorrale\Desktop\Models_running\IPPU_2025_01_14\A1_Outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IgnacioAlfaroCorrale\Desktop\Models_running\IPPU_hfc_desglose\A1_Outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56AEB947-9DA8-4E76-B88D-0881BE537DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473122C0-6E2B-4851-97BD-BCAAD85354A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -394,7 +394,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -437,9 +437,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -997,82 +997,82 @@
         <v>0</v>
       </c>
       <c r="I3" s="6">
-        <v>0.21490000000000001</v>
+        <v>0</v>
       </c>
       <c r="J3" s="6">
-        <v>0.252</v>
+        <v>0</v>
       </c>
       <c r="K3" s="6">
-        <v>0.28910000000000002</v>
+        <v>0</v>
       </c>
       <c r="L3" s="6">
-        <v>0.33179999999999998</v>
+        <v>0</v>
       </c>
       <c r="M3" s="6">
-        <v>0.3745</v>
+        <v>0</v>
       </c>
       <c r="N3" s="6">
-        <v>0.42370000000000002</v>
+        <v>0</v>
       </c>
       <c r="O3" s="6">
-        <v>0.47289999999999999</v>
+        <v>0</v>
       </c>
       <c r="P3" s="6">
-        <v>0.496</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="6">
-        <v>0.51910000000000001</v>
+        <v>0</v>
       </c>
       <c r="R3" s="6">
-        <v>0.86109999999999998</v>
+        <v>0</v>
       </c>
       <c r="S3" s="6">
-        <v>1.2030000000000001</v>
+        <v>0</v>
       </c>
       <c r="T3" s="6">
-        <v>1.3250999999999999</v>
+        <v>0</v>
       </c>
       <c r="U3" s="6">
-        <v>1.9576</v>
+        <v>0</v>
       </c>
       <c r="V3" s="6">
-        <v>2.3839999999999999</v>
+        <v>0</v>
       </c>
       <c r="W3" s="6">
-        <v>2.8102999999999998</v>
+        <v>0</v>
       </c>
       <c r="X3" s="6">
-        <v>3.2366999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="6">
-        <v>3.6631</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="6">
-        <v>4.0895000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="6">
-        <v>4.5159000000000002</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="6">
-        <v>4.9421999999999997</v>
+        <v>0</v>
       </c>
       <c r="AC3" s="6">
-        <v>5.3685999999999998</v>
+        <v>0</v>
       </c>
       <c r="AD3" s="6">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="6">
-        <v>5.3913000000000002</v>
+        <v>0</v>
       </c>
       <c r="AF3" s="6">
-        <v>5.4025999999999996</v>
+        <v>0</v>
       </c>
       <c r="AG3" s="6">
-        <v>5.4139999999999997</v>
+        <v>0</v>
       </c>
       <c r="AH3" s="6">
-        <v>5.4253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.3">
@@ -1100,83 +1100,83 @@
       <c r="H4" s="3">
         <v>0</v>
       </c>
-      <c r="I4" s="8">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8">
-        <v>0</v>
-      </c>
-      <c r="K4" s="8">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8">
-        <v>0</v>
-      </c>
-      <c r="N4" s="8">
-        <v>0</v>
-      </c>
-      <c r="O4" s="8">
-        <v>0</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0</v>
-      </c>
-      <c r="R4" s="8">
-        <v>0</v>
-      </c>
-      <c r="S4" s="8">
-        <v>0</v>
-      </c>
-      <c r="T4" s="8">
-        <v>0</v>
-      </c>
-      <c r="U4" s="8">
-        <v>0</v>
-      </c>
-      <c r="V4" s="8">
-        <v>0</v>
-      </c>
-      <c r="W4" s="8">
-        <v>0</v>
-      </c>
-      <c r="X4" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="8">
-        <v>0</v>
+      <c r="I4" s="10">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="J4" s="10">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="K4" s="10">
+        <v>2E-3</v>
+      </c>
+      <c r="L4" s="10">
+        <v>1.5E-3</v>
+      </c>
+      <c r="M4" s="10">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="N4" s="10">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="O4" s="10">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="P4" s="10">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="Q4" s="10">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="R4" s="10">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="S4" s="10">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="T4" s="10">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="U4" s="10">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="V4" s="10">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="W4" s="10">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="X4" s="10">
+        <v>1E-3</v>
+      </c>
+      <c r="Y4" s="10">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Z4" s="10">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="AA4" s="10">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AB4" s="10">
+        <v>1.5E-3</v>
+      </c>
+      <c r="AC4" s="10">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="AD4" s="10">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="AE4" s="10">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="AF4" s="10">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="AG4" s="10">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="AH4" s="10">
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
@@ -1204,83 +1204,83 @@
       <c r="H5" s="3">
         <v>0</v>
       </c>
-      <c r="I5" s="8">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8">
-        <v>0</v>
-      </c>
-      <c r="K5" s="8">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8">
-        <v>0</v>
-      </c>
-      <c r="N5" s="8">
-        <v>0</v>
-      </c>
-      <c r="O5" s="8">
-        <v>0</v>
-      </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>0</v>
-      </c>
-      <c r="R5" s="8">
-        <v>0</v>
-      </c>
-      <c r="S5" s="8">
-        <v>0</v>
-      </c>
-      <c r="T5" s="8">
-        <v>0</v>
-      </c>
-      <c r="U5" s="8">
-        <v>0</v>
-      </c>
-      <c r="V5" s="8">
-        <v>0</v>
-      </c>
-      <c r="W5" s="8">
-        <v>0</v>
-      </c>
-      <c r="X5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="8">
-        <v>0</v>
+      <c r="I5" s="10">
+        <v>4.3E-3</v>
+      </c>
+      <c r="J5" s="10">
+        <v>3.8E-3</v>
+      </c>
+      <c r="K5" s="10">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="L5" s="10">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="M5" s="10">
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="N5" s="10">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="O5" s="10">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="P5" s="10">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="R5" s="10">
+        <v>2.3199999999999998E-2</v>
+      </c>
+      <c r="S5" s="10">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="T5" s="10">
+        <v>4.7899999999999998E-2</v>
+      </c>
+      <c r="U5" s="10">
+        <v>7.3700000000000002E-2</v>
+      </c>
+      <c r="V5" s="10">
+        <v>8.9800000000000005E-2</v>
+      </c>
+      <c r="W5" s="10">
+        <v>0.10589999999999999</v>
+      </c>
+      <c r="X5" s="10">
+        <v>0.122</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>0.1381</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>0.15409999999999999</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>0.17019999999999999</v>
+      </c>
+      <c r="AB5" s="10">
+        <v>0.18629999999999999</v>
+      </c>
+      <c r="AC5" s="10">
+        <v>0.20230000000000001</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>0.20280000000000001</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>0.20319999999999999</v>
+      </c>
+      <c r="AF5" s="10">
+        <v>0.2036</v>
+      </c>
+      <c r="AG5" s="10">
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="AH5" s="10">
+        <v>0.20449999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
@@ -1308,83 +1308,83 @@
       <c r="H6" s="3">
         <v>0</v>
       </c>
-      <c r="I6" s="8">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8">
-        <v>0</v>
-      </c>
-      <c r="K6" s="8">
-        <v>0</v>
-      </c>
-      <c r="L6" s="8">
-        <v>0</v>
-      </c>
-      <c r="M6" s="8">
-        <v>0</v>
-      </c>
-      <c r="N6" s="8">
-        <v>0</v>
-      </c>
-      <c r="O6" s="8">
-        <v>0</v>
-      </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>0</v>
-      </c>
-      <c r="R6" s="8">
-        <v>0</v>
-      </c>
-      <c r="S6" s="8">
-        <v>0</v>
-      </c>
-      <c r="T6" s="8">
-        <v>0</v>
-      </c>
-      <c r="U6" s="8">
-        <v>0</v>
-      </c>
-      <c r="V6" s="8">
-        <v>0</v>
-      </c>
-      <c r="W6" s="8">
-        <v>0</v>
-      </c>
-      <c r="X6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="8">
-        <v>0</v>
+      <c r="I6" s="10">
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="J6" s="10">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="K6" s="10">
+        <v>1.26E-2</v>
+      </c>
+      <c r="L6" s="10">
+        <v>1.37E-2</v>
+      </c>
+      <c r="M6" s="10">
+        <v>1.01E-2</v>
+      </c>
+      <c r="N6" s="10">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="O6" s="10">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="P6" s="10">
+        <v>6.3E-3</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>6.7999999999999996E-3</v>
+      </c>
+      <c r="R6" s="10">
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="S6" s="10">
+        <v>9.5399999999999999E-2</v>
+      </c>
+      <c r="T6" s="10">
+        <v>0.1172</v>
+      </c>
+      <c r="U6" s="10">
+        <v>0.18540000000000001</v>
+      </c>
+      <c r="V6" s="10">
+        <v>0.2258</v>
+      </c>
+      <c r="W6" s="10">
+        <v>0.26619999999999999</v>
+      </c>
+      <c r="X6" s="10">
+        <v>0.30659999999999998</v>
+      </c>
+      <c r="Y6" s="10">
+        <v>0.34689999999999999</v>
+      </c>
+      <c r="Z6" s="10">
+        <v>0.38729999999999998</v>
+      </c>
+      <c r="AA6" s="10">
+        <v>0.42770000000000002</v>
+      </c>
+      <c r="AB6" s="10">
+        <v>0.46810000000000002</v>
+      </c>
+      <c r="AC6" s="10">
+        <v>0.50849999999999995</v>
+      </c>
+      <c r="AD6" s="10">
+        <v>0.50960000000000005</v>
+      </c>
+      <c r="AE6" s="10">
+        <v>0.51060000000000005</v>
+      </c>
+      <c r="AF6" s="10">
+        <v>0.51170000000000004</v>
+      </c>
+      <c r="AG6" s="10">
+        <v>0.51280000000000003</v>
+      </c>
+      <c r="AH6" s="10">
+        <v>0.51390000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
@@ -1412,83 +1412,83 @@
       <c r="H7" s="3">
         <v>0</v>
       </c>
-      <c r="I7" s="8">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8">
-        <v>0</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8">
-        <v>0</v>
-      </c>
-      <c r="N7" s="8">
-        <v>0</v>
-      </c>
-      <c r="O7" s="8">
-        <v>0</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
-        <v>0</v>
-      </c>
-      <c r="S7" s="8">
-        <v>0</v>
-      </c>
-      <c r="T7" s="8">
-        <v>0</v>
-      </c>
-      <c r="U7" s="8">
-        <v>0</v>
-      </c>
-      <c r="V7" s="8">
-        <v>0</v>
-      </c>
-      <c r="W7" s="8">
-        <v>0</v>
-      </c>
-      <c r="X7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="8">
-        <v>0</v>
+      <c r="I7" s="10">
+        <v>7.9399999999999998E-2</v>
+      </c>
+      <c r="J7" s="10">
+        <v>9.06E-2</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0.1235</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0.1658</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0.22550000000000001</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0.27650000000000002</v>
+      </c>
+      <c r="O7" s="10">
+        <v>0.30719999999999997</v>
+      </c>
+      <c r="P7" s="10">
+        <v>0.3382</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>0.36280000000000001</v>
+      </c>
+      <c r="R7" s="10">
+        <v>0.39779999999999999</v>
+      </c>
+      <c r="S7" s="10">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="T7" s="10">
+        <v>0.41220000000000001</v>
+      </c>
+      <c r="U7" s="10">
+        <v>0.46910000000000002</v>
+      </c>
+      <c r="V7" s="10">
+        <v>0.57130000000000003</v>
+      </c>
+      <c r="W7" s="10">
+        <v>0.67349999999999999</v>
+      </c>
+      <c r="X7" s="10">
+        <v>0.77569999999999995</v>
+      </c>
+      <c r="Y7" s="10">
+        <v>0.87780000000000002</v>
+      </c>
+      <c r="Z7" s="10">
+        <v>0.98</v>
+      </c>
+      <c r="AA7" s="10">
+        <v>1.0822000000000001</v>
+      </c>
+      <c r="AB7" s="10">
+        <v>1.1843999999999999</v>
+      </c>
+      <c r="AC7" s="10">
+        <v>1.2865</v>
+      </c>
+      <c r="AD7" s="10">
+        <v>1.2892999999999999</v>
+      </c>
+      <c r="AE7" s="10">
+        <v>1.292</v>
+      </c>
+      <c r="AF7" s="10">
+        <v>1.2947</v>
+      </c>
+      <c r="AG7" s="10">
+        <v>1.2974000000000001</v>
+      </c>
+      <c r="AH7" s="10">
+        <v>1.3001</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.3">
@@ -1516,83 +1516,83 @@
       <c r="H8" s="3">
         <v>0</v>
       </c>
-      <c r="I8" s="8">
-        <v>0</v>
-      </c>
-      <c r="J8" s="8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="8">
-        <v>0</v>
-      </c>
-      <c r="L8" s="8">
-        <v>0</v>
-      </c>
-      <c r="M8" s="8">
-        <v>0</v>
-      </c>
-      <c r="N8" s="8">
-        <v>0</v>
-      </c>
-      <c r="O8" s="8">
-        <v>0</v>
-      </c>
-      <c r="P8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>0</v>
-      </c>
-      <c r="R8" s="8">
-        <v>0</v>
-      </c>
-      <c r="S8" s="8">
-        <v>0</v>
-      </c>
-      <c r="T8" s="8">
-        <v>0</v>
-      </c>
-      <c r="U8" s="8">
-        <v>0</v>
-      </c>
-      <c r="V8" s="8">
-        <v>0</v>
-      </c>
-      <c r="W8" s="8">
-        <v>0</v>
-      </c>
-      <c r="X8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="8">
-        <v>0</v>
+      <c r="I8" s="10">
+        <v>7.7999999999999996E-3</v>
+      </c>
+      <c r="J8" s="10">
+        <v>1.09E-2</v>
+      </c>
+      <c r="K8" s="10">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="L8" s="10">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="M8" s="10">
+        <v>6.3E-3</v>
+      </c>
+      <c r="N8" s="10">
+        <v>8.6E-3</v>
+      </c>
+      <c r="O8" s="10">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="P8" s="10">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="R8" s="10">
+        <v>4.0899999999999999E-2</v>
+      </c>
+      <c r="S8" s="10">
+        <v>6.6199999999999995E-2</v>
+      </c>
+      <c r="T8" s="10">
+        <v>7.9699999999999993E-2</v>
+      </c>
+      <c r="U8" s="10">
+        <v>0.1464</v>
+      </c>
+      <c r="V8" s="10">
+        <v>0.17829999999999999</v>
+      </c>
+      <c r="W8" s="10">
+        <v>0.21010000000000001</v>
+      </c>
+      <c r="X8" s="10">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="Y8" s="10">
+        <v>0.27389999999999998</v>
+      </c>
+      <c r="Z8" s="10">
+        <v>0.30580000000000002</v>
+      </c>
+      <c r="AA8" s="10">
+        <v>0.3377</v>
+      </c>
+      <c r="AB8" s="10">
+        <v>0.36959999999999998</v>
+      </c>
+      <c r="AC8" s="10">
+        <v>0.40139999999999998</v>
+      </c>
+      <c r="AD8" s="10">
+        <v>0.40229999999999999</v>
+      </c>
+      <c r="AE8" s="10">
+        <v>0.40310000000000001</v>
+      </c>
+      <c r="AF8" s="10">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="AG8" s="10">
+        <v>0.40479999999999999</v>
+      </c>
+      <c r="AH8" s="10">
+        <v>0.40570000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.3">
@@ -1620,83 +1620,83 @@
       <c r="H9" s="3">
         <v>0</v>
       </c>
-      <c r="I9" s="8">
-        <v>0</v>
-      </c>
-      <c r="J9" s="8">
-        <v>0</v>
-      </c>
-      <c r="K9" s="8">
-        <v>0</v>
-      </c>
-      <c r="L9" s="8">
-        <v>0</v>
-      </c>
-      <c r="M9" s="8">
-        <v>0</v>
-      </c>
-      <c r="N9" s="8">
-        <v>0</v>
-      </c>
-      <c r="O9" s="8">
-        <v>0</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
-        <v>0</v>
-      </c>
-      <c r="S9" s="8">
-        <v>0</v>
-      </c>
-      <c r="T9" s="8">
-        <v>0</v>
-      </c>
-      <c r="U9" s="8">
-        <v>0</v>
-      </c>
-      <c r="V9" s="8">
-        <v>0</v>
-      </c>
-      <c r="W9" s="8">
-        <v>0</v>
-      </c>
-      <c r="X9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="8">
-        <v>0</v>
+      <c r="I9" s="10">
+        <v>0</v>
+      </c>
+      <c r="J9" s="10">
+        <v>0</v>
+      </c>
+      <c r="K9" s="10">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="M9" s="10">
+        <v>1.4E-3</v>
+      </c>
+      <c r="N9" s="10">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="O9" s="10">
+        <v>1.4E-3</v>
+      </c>
+      <c r="P9" s="10">
+        <v>1.4E-3</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="R9" s="10">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="S9" s="10">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="T9" s="10">
+        <v>1.4E-3</v>
+      </c>
+      <c r="U9" s="10">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="V9" s="10">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="W9" s="10">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="X9" s="10">
+        <v>3.3E-3</v>
+      </c>
+      <c r="Y9" s="10">
+        <v>3.8E-3</v>
+      </c>
+      <c r="Z9" s="10">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="AA9" s="10">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="AB9" s="10">
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="AC9" s="10">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="AD9" s="10">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="AE9" s="10">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="AF9" s="10">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="AG9" s="10">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="AH9" s="10">
+        <v>5.5999999999999999E-3</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.3">
@@ -1724,82 +1724,82 @@
       <c r="H10" s="3">
         <v>0</v>
       </c>
-      <c r="I10" s="8">
-        <v>0</v>
-      </c>
-      <c r="J10" s="8">
-        <v>0</v>
-      </c>
-      <c r="K10" s="8">
-        <v>0</v>
-      </c>
-      <c r="L10" s="8">
-        <v>0</v>
-      </c>
-      <c r="M10" s="8">
-        <v>0</v>
-      </c>
-      <c r="N10" s="8">
-        <v>0</v>
-      </c>
-      <c r="O10" s="8">
-        <v>0</v>
-      </c>
-      <c r="P10" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
-        <v>0</v>
-      </c>
-      <c r="S10" s="8">
-        <v>0</v>
-      </c>
-      <c r="T10" s="8">
-        <v>0</v>
-      </c>
-      <c r="U10" s="8">
-        <v>0</v>
-      </c>
-      <c r="V10" s="8">
-        <v>0</v>
-      </c>
-      <c r="W10" s="8">
-        <v>0</v>
-      </c>
-      <c r="X10" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="8">
+      <c r="I10" s="6">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6">
+        <v>0</v>
+      </c>
+      <c r="L10" s="6">
+        <v>0</v>
+      </c>
+      <c r="M10" s="6">
+        <v>0</v>
+      </c>
+      <c r="N10" s="6">
+        <v>0</v>
+      </c>
+      <c r="O10" s="6">
+        <v>0</v>
+      </c>
+      <c r="P10" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>0</v>
+      </c>
+      <c r="R10" s="6">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6">
+        <v>0</v>
+      </c>
+      <c r="T10" s="6">
+        <v>0</v>
+      </c>
+      <c r="U10" s="6">
+        <v>0</v>
+      </c>
+      <c r="V10" s="6">
+        <v>0</v>
+      </c>
+      <c r="W10" s="6">
+        <v>0</v>
+      </c>
+      <c r="X10" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2740,60 +2740,60 @@
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="9"/>
-      <c r="U22" s="9"/>
-      <c r="V22" s="9"/>
-      <c r="W22" s="9"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="9"/>
-      <c r="Z22" s="9"/>
-      <c r="AA22" s="9"/>
-      <c r="AB22" s="9"/>
-      <c r="AC22" s="9"/>
-      <c r="AD22" s="9"/>
-      <c r="AE22" s="9"/>
-      <c r="AF22" s="9"/>
-      <c r="AG22" s="9"/>
-      <c r="AH22" s="9"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+      <c r="V22" s="8"/>
+      <c r="W22" s="8"/>
+      <c r="X22" s="8"/>
+      <c r="Y22" s="8"/>
+      <c r="Z22" s="8"/>
+      <c r="AA22" s="8"/>
+      <c r="AB22" s="8"/>
+      <c r="AC22" s="8"/>
+      <c r="AD22" s="8"/>
+      <c r="AE22" s="8"/>
+      <c r="AF22" s="8"/>
+      <c r="AG22" s="8"/>
+      <c r="AH22" s="8"/>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
-      <c r="S23" s="10"/>
-      <c r="T23" s="10"/>
-      <c r="U23" s="10"/>
-      <c r="V23" s="10"/>
-      <c r="W23" s="10"/>
-      <c r="X23" s="10"/>
-      <c r="Y23" s="10"/>
-      <c r="Z23" s="10"/>
-      <c r="AA23" s="10"/>
-      <c r="AB23" s="10"/>
-      <c r="AC23" s="10"/>
-      <c r="AD23" s="10"/>
-      <c r="AE23" s="10"/>
-      <c r="AF23" s="10"/>
-      <c r="AG23" s="10"/>
-      <c r="AH23" s="10"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="9"/>
+      <c r="AG23" s="9"/>
+      <c r="AH23" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AH11" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -2803,21 +2803,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B8F814574E960A4499025803604D4DF4" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="314e7041d7d1561dbe33e80becf1c782">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b2ff61d-e0c4-454b-ba72-44cf85c32a41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="84c838da6aa04a0f137f8b0aba02cfe1" ns2:_="">
     <xsd:import namespace="4b2ff61d-e0c4-454b-ba72-44cf85c32a41"/>
@@ -2987,24 +2972,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DB55C3E-F740-40DC-A110-0B8D499DD44E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBC1D0AD-7548-4EBE-9E7D-341DF4908EC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{818B3588-4A65-45B4-B0A9-14434EB18F0C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3020,4 +3003,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DB55C3E-F740-40DC-A110-0B8D499DD44E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBC1D0AD-7548-4EBE-9E7D-341DF4908EC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>